--- a/MixMaster.xlsx
+++ b/MixMaster.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KEIYA\Documents\GitHub\MixMaster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDAD0B0E-5540-42DA-BE1C-92DD8D3A14B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FAA914-7B79-4CC2-A108-9560C56E57A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5B45C5E-FDA1-433E-B65D-DA276FD740E0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="モンスター" sheetId="3" r:id="rId1"/>
+    <sheet name="画像編集用" sheetId="1" r:id="rId2"/>
+    <sheet name="仕様メモ" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,9 +40,2225 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="426">
+  <si>
+    <t>各マップに祭壇が設置されていて各モンスター用の強化項目がある。</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップ率は最大強化時に10％になるようにする(要検討)</t>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ヨウケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スポーン間隔は初期値はEnemySOをもとに設定。最大強化で0になり、倒した瞬間に次がリポップするようになる。</t>
+    <rPh sb="4" eb="6">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シュンカン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターのドロップは初期値は超低確率。</t>
+    <rPh sb="11" eb="14">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターの固有素材を供えるとそのモンスターのスポーン間隔とドロップ率が強化される。</t>
+    <rPh sb="6" eb="10">
+      <t>コユウソザイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ソナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>祭壇は最大レベル後、リポップ間隔とドロップ率をsliderかボタンでいじれるようにする。(最大強化でリポップしないようにすることもできるようにする。)</t>
+    <rPh sb="0" eb="2">
+      <t>サイダン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターの素材はEnemySOのドロップ率をもとに1つドロップする。敵を倒したプレイヤーや仲間モンスターのドロップ率加算によって100％を超える度にドロップ数が増えていき、余った％でもう一つドロップするか抽選される。</t>
+    <rPh sb="6" eb="8">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ナカマ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>タビ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>チュウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（例）ドロップ率10％の素材に対して倒した仲間モンスターやプレイヤーのドロップ率が200％なら、２個確定でドロップして10％の確率で3個目がドロップする。</t>
+    <rPh sb="1" eb="2">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナカマ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>稀に称号付きモンスターがドロップすることがある。称号は同じマップにいるモンスターの所持称号からランダムで1つ付与される。</t>
+    <rPh sb="0" eb="1">
+      <t>マレ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>称号が付くとステータスに％補正がかかる。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・モンスターと素材のドロップ、祭壇</t>
+    <rPh sb="7" eb="9">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サイダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・モンスターの成長</t>
+    <rPh sb="7" eb="9">
+      <t>セイチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎ステータス×レベルで算出する。</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベルが1上がると基礎ステータス分ステータスが上がる。スキルポイントも取得できる。</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個体値も存在し、各ステータスに0～100段階の補正値が存在する。0で半分50で*1、100で1.5倍</t>
+    <rPh sb="0" eb="2">
+      <t>コタイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ホセイチ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・モンスターの行動</t>
+    <rPh sb="7" eb="9">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルはスキルポイントを消費して獲得する。モンスターごとにスキルは設定する。</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離攻撃と遠距離攻撃が存在する。</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離なら魔力参照の魔弾を発射する。</t>
+    <rPh sb="0" eb="3">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離なら攻撃参照の斬撃を発動。</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ザンゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・配合</t>
+    <rPh sb="1" eb="3">
+      <t>ハイゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両親どちらかの称号と個体値を引き継いで誕生する。</t>
+    <rPh sb="0" eb="2">
+      <t>リョウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>両親は消える。</t>
+    <rPh sb="0" eb="2">
+      <t>リョウシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルポイント（両親が消費した分）も引き継ぐ。</t>
+    <rPh sb="8" eb="10">
+      <t>リョウシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルもランダムで３つ引き継ぐ</t>
+    <rPh sb="11" eb="12">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各マップにはダンジョンが存在する。</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダンジョンの宝箱からは装備とダンジョン限定素材がドロップする。</t>
+    <rPh sb="6" eb="8">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダンジョンに現れる敵からも低確率でドロップする。</t>
+    <rPh sb="6" eb="7">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>テイカクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１ダンジョンに付き装備種は1つ。</t>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダンジョンに現れる敵は外マップのモンスター達が部屋に入った瞬間にスポーンする</t>
+    <rPh sb="6" eb="7">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ダンジョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備は装着するとステータスに割合補正が入る。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウチャク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ワリアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正方形の部屋を通路でつなげたような構造にし、周回しやすくする。</t>
+    <rPh sb="0" eb="3">
+      <t>セイホウケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウロ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのマップのダンジョン限定素材でこのマップのモンスターの称号付与率を上げることができる。</t>
+    <rPh sb="11" eb="13">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ショウゴウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備はプレイヤーと仲間共に3つまでにする。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナカマ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ステータス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルも大量に制作し、モンスターごとに１０個ほど割り当てる。</t>
+    <rPh sb="4" eb="6">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・転生</t>
+    <rPh sb="1" eb="3">
+      <t>テンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー限定で転生できる。</t>
+    <rPh sb="5" eb="7">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>転生書は味方モンスターに親密度を設定し、それがカンストしたらそのモンスターの基礎値と所持しているスキルを参照して転生書が作成される。</t>
+    <rPh sb="0" eb="2">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シンミツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP　Long</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力　Long</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔力　Long</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防御力　Long</t>
+    <rPh sb="0" eb="3">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法防御力　Long</t>
+    <rPh sb="0" eb="5">
+      <t>マホウボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリティカル率　Float</t>
+    <rPh sb="6" eb="7">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリティカル倍率　Float</t>
+    <rPh sb="6" eb="8">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃速度　Float　（初期値に倍率を掛けるようにする150％なら1.5倍速って感じ。）</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>バイソク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度　Float　（初期値に倍率をかけるようにする150％なら1.5倍速って感じ。）</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各種属性耐性Float（-1000％から80％の範囲で設定。最大80％カット）</t>
+    <rPh sb="0" eb="2">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップ率アップ　Float（加算式。元のドロップ率に加算する。）</t>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ステータスはプレイヤーとモンスター共通で
+HP、攻撃力、魔力、防御力、魔法防御力、クリティカル率、クリティカル倍率、移動速度、攻撃速度、各種属性耐性、属性
+プレイヤーと味方モンスター限定で
+ドロップ率アップ（装備で上げることになる）
+(属性は攻撃に属性が付与されて属性耐性によって最終値がダメージ計算される)</t>
+    <rPh sb="76" eb="78">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性　Bool　（敵味方モンスターに共通して攻撃がこの属性になる。ダメージ計算の最終値に各種属性耐性を参照した数値を掛ける。プレイヤーは転生後、消費した転生書に応じて属性攻撃ができるようになる。）</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>テキミカタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベルが１に戻り転生書を消費した場合転生書に記載されている基礎値とスキル、属性を所持した状態で転生する。</t>
+    <rPh sb="6" eb="7">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>テンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>転生の利点はスキルポイントが引き継げることと好きなモンスターと同じ成長の仕方をできること、属性を変えられること。</t>
+    <rPh sb="0" eb="2">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リテン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイチョウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シカタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MP　Long</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブルースライム</t>
+  </si>
+  <si>
+    <t>レッドスライム</t>
+  </si>
+  <si>
+    <t>グリーンスライム</t>
+  </si>
+  <si>
+    <t>レッドボア</t>
+  </si>
+  <si>
+    <t>ブルーボア</t>
+  </si>
+  <si>
+    <t>スライムフォース</t>
+  </si>
+  <si>
+    <t>ゴブリン</t>
+  </si>
+  <si>
+    <t>ゴブリンウォーリアー</t>
+  </si>
+  <si>
+    <t>ゴブリンメイジ</t>
+  </si>
+  <si>
+    <t>ボブゴブリン</t>
+  </si>
+  <si>
+    <t>マテリアスライム</t>
+  </si>
+  <si>
+    <t>ゴブリンキング</t>
+  </si>
+  <si>
+    <t>ルーインズスラッグ</t>
+  </si>
+  <si>
+    <t>ライティングスラッグ</t>
+  </si>
+  <si>
+    <t>幽霊</t>
+  </si>
+  <si>
+    <t>怨念</t>
+  </si>
+  <si>
+    <t>ドラゴンゾンビ</t>
+  </si>
+  <si>
+    <t>エクリス・カース</t>
+  </si>
+  <si>
+    <t>コボルト</t>
+  </si>
+  <si>
+    <t>ウルフ</t>
+  </si>
+  <si>
+    <t>ブラッドウルフ</t>
+  </si>
+  <si>
+    <t>人狼</t>
+  </si>
+  <si>
+    <t>ラグナ・ヴォルグ</t>
+  </si>
+  <si>
+    <t>ヴォルグ・スカー</t>
+  </si>
+  <si>
+    <t>ドレッドハンター</t>
+  </si>
+  <si>
+    <t>アシッドスライム</t>
+  </si>
+  <si>
+    <t>浮遊甲冑</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カッチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グラーヴナイト</t>
+  </si>
+  <si>
+    <t>ネクロウィスプ</t>
+  </si>
+  <si>
+    <t>ボーンアバドン</t>
+  </si>
+  <si>
+    <t>スケルトン</t>
+  </si>
+  <si>
+    <t>サンドワーム</t>
+  </si>
+  <si>
+    <t>ブラックサンドワーム</t>
+  </si>
+  <si>
+    <t>ブラックコボルト</t>
+  </si>
+  <si>
+    <t>ヴォルドーム</t>
+  </si>
+  <si>
+    <t>ラヴァスコール</t>
+  </si>
+  <si>
+    <t>魔法使い</t>
+  </si>
+  <si>
+    <t>魔女</t>
+  </si>
+  <si>
+    <t>カーラ＆ヴィクトリア</t>
+  </si>
+  <si>
+    <t>セリウス・アークレイン</t>
+  </si>
+  <si>
+    <t>マグナ・アルセリオン</t>
+  </si>
+  <si>
+    <t>アルカ・マギウス</t>
+  </si>
+  <si>
+    <t>ゴーレムナイト</t>
+  </si>
+  <si>
+    <t>溶岩魔人</t>
+  </si>
+  <si>
+    <t>蒼溶岩魔人</t>
+  </si>
+  <si>
+    <t>魔人の土偶</t>
+  </si>
+  <si>
+    <t>グラヴィアズール</t>
+  </si>
+  <si>
+    <t>ヴォルザロック</t>
+  </si>
+  <si>
+    <t>ゴーレムガーディアン</t>
+  </si>
+  <si>
+    <t>シルバーゴーレム</t>
+  </si>
+  <si>
+    <t>ゴールドゴーレム</t>
+  </si>
+  <si>
+    <t>シルバースライム</t>
+  </si>
+  <si>
+    <t>アストラ・コロッサス</t>
+  </si>
+  <si>
+    <t>グラヴェルノス</t>
+  </si>
+  <si>
+    <t>ファイヤリザード</t>
+  </si>
+  <si>
+    <t>サイクロプス</t>
+  </si>
+  <si>
+    <t>ソルドリム・アイアンハート</t>
+  </si>
+  <si>
+    <t>ヴァルサイクロプス</t>
+  </si>
+  <si>
+    <t>グラウンドタイタン</t>
+  </si>
+  <si>
+    <t>煌獄騎デュザリオン</t>
+  </si>
+  <si>
+    <t>ゴーレムメーカー</t>
+  </si>
+  <si>
+    <t>リヴィア・ハートライン</t>
+  </si>
+  <si>
+    <t>アクア・レギュレイター</t>
+  </si>
+  <si>
+    <t>フォレスト・ガンナー</t>
+  </si>
+  <si>
+    <t>レジスト・ゴレイオン</t>
+  </si>
+  <si>
+    <t>インフェルノ・ギア</t>
+  </si>
+  <si>
+    <t>サラマンダー</t>
+  </si>
+  <si>
+    <t>赤竜</t>
+  </si>
+  <si>
+    <t>エンシェント・レッド</t>
+  </si>
+  <si>
+    <t>ヴァルイグニス</t>
+  </si>
+  <si>
+    <t>ヘルグラッド</t>
+  </si>
+  <si>
+    <t>グラン・スライオス</t>
+  </si>
+  <si>
+    <t>スイマーゴブリン</t>
+  </si>
+  <si>
+    <t>漕手ゴブリン</t>
+  </si>
+  <si>
+    <t>メガロドン</t>
+  </si>
+  <si>
+    <t>ブルオメガ</t>
+  </si>
+  <si>
+    <t>ネプチ・アブル</t>
+  </si>
+  <si>
+    <t>アビサル・ネプトゥス</t>
+  </si>
+  <si>
+    <t>狩猟ゴブリン</t>
+  </si>
+  <si>
+    <t>フェアリー</t>
+  </si>
+  <si>
+    <t>長老ゴブリン</t>
+  </si>
+  <si>
+    <t>リザ・ヴァルク</t>
+  </si>
+  <si>
+    <t>ボル・グルナ</t>
+  </si>
+  <si>
+    <t>ガル・フェンリオ</t>
+  </si>
+  <si>
+    <t>人食いキノコ</t>
+  </si>
+  <si>
+    <t>ゴールドスライム</t>
+  </si>
+  <si>
+    <t>スライムキング</t>
+  </si>
+  <si>
+    <t>マグ・スライム</t>
+  </si>
+  <si>
+    <t>キング・グリット</t>
+  </si>
+  <si>
+    <t>ルクス・ジェリー</t>
+  </si>
+  <si>
+    <t>キラーマンティス</t>
+  </si>
+  <si>
+    <t>スタグビートル</t>
+  </si>
+  <si>
+    <t>キラーセンチピード</t>
+  </si>
+  <si>
+    <t>ヴェス・カリバー</t>
+  </si>
+  <si>
+    <t>インフェル・ビートル</t>
+  </si>
+  <si>
+    <t>ルミナ・ミラージュ</t>
+  </si>
+  <si>
+    <t>ラストコア</t>
+  </si>
+  <si>
+    <t>ターミナス・ギアロード</t>
+  </si>
+  <si>
+    <t>インフェルナル・オーバードライブ</t>
+  </si>
+  <si>
+    <t>ブルー・ヴォルテクス</t>
+  </si>
+  <si>
+    <t>マグナ・ギアゴーレム</t>
+  </si>
+  <si>
+    <t>アーク・セラフィオン</t>
+  </si>
+  <si>
+    <t>ラグス</t>
+  </si>
+  <si>
+    <t>バルド</t>
+  </si>
+  <si>
+    <t>バルザック</t>
+  </si>
+  <si>
+    <t>ゴルダン</t>
+  </si>
+  <si>
+    <t>カーンヴァル</t>
+  </si>
+  <si>
+    <t>グリモルダン</t>
+  </si>
+  <si>
+    <t>ライトワーム</t>
+  </si>
+  <si>
+    <t>ケイブスパイダー</t>
+  </si>
+  <si>
+    <t>亡霊鉱夫</t>
+    <rPh sb="0" eb="2">
+      <t>ボウレイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オット</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイコドレイク</t>
+  </si>
+  <si>
+    <t>アースドラゴン</t>
+  </si>
+  <si>
+    <t>アビスドラゴン</t>
+  </si>
+  <si>
+    <t>フィローナ</t>
+  </si>
+  <si>
+    <t>キューㇾリス</t>
+  </si>
+  <si>
+    <t>コランチュラ</t>
+  </si>
+  <si>
+    <t>ダルンドゥ</t>
+  </si>
+  <si>
+    <t>ガルブロッサ</t>
+  </si>
+  <si>
+    <t>ドレインタス</t>
+  </si>
+  <si>
+    <t>スカイレイヴン</t>
+  </si>
+  <si>
+    <t>ガレウィングホーク</t>
+  </si>
+  <si>
+    <t>フェザードヴァルチャー</t>
+  </si>
+  <si>
+    <t>ハーピー</t>
+  </si>
+  <si>
+    <t>ストームコンドル</t>
+  </si>
+  <si>
+    <t>アル・ヴォレオス</t>
+  </si>
+  <si>
+    <t>魔導覇鬼ゴルヴァス</t>
+  </si>
+  <si>
+    <t>マキナレクス</t>
+  </si>
+  <si>
+    <t>ヴェルザーク</t>
+  </si>
+  <si>
+    <t>灼岩王グレアラグ</t>
+    <rPh sb="0" eb="1">
+      <t>シャク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ガン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アヴィドゥス・マグマ―ル</t>
+  </si>
+  <si>
+    <t>雷牙王ヴァルドゥーン</t>
+    <rPh sb="0" eb="1">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キバ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネグロスパイダー</t>
+  </si>
+  <si>
+    <t>リッチ・モルディガン</t>
+  </si>
+  <si>
+    <t>ネクロ・ドラグニル</t>
+  </si>
+  <si>
+    <t>ヴァル・ディアブロ</t>
+  </si>
+  <si>
+    <t>ブラッド・ミノタウロス</t>
+  </si>
+  <si>
+    <t>アズラ・ヒュドラ</t>
+  </si>
+  <si>
+    <t>マグ・ヴォルム</t>
+  </si>
+  <si>
+    <t>フロスティア・レクイエム</t>
+  </si>
+  <si>
+    <t>インフェルノ・バルガス</t>
+  </si>
+  <si>
+    <t>ネフェル・アンムート</t>
+  </si>
+  <si>
+    <t>ヴァル・ノクティス</t>
+  </si>
+  <si>
+    <t>モル・カヴァリエ</t>
+  </si>
+  <si>
+    <t>グリーン・カタストラ</t>
+  </si>
+  <si>
+    <t>タラッサ・ミルディア</t>
+  </si>
+  <si>
+    <t>スカルロード</t>
+  </si>
+  <si>
+    <t>アシュタロス・リリア</t>
+  </si>
+  <si>
+    <t>ブッチャー・ゴルム</t>
+  </si>
+  <si>
+    <t>ヴォイド・バルザーク</t>
+  </si>
+  <si>
+    <t>錆びた坑夫スケルトン</t>
+  </si>
+  <si>
+    <t>掘削ゴブリン</t>
+  </si>
+  <si>
+    <t>鉄屑スライム</t>
+  </si>
+  <si>
+    <t>崩落モール</t>
+  </si>
+  <si>
+    <t>煤まみれの幽霊</t>
+  </si>
+  <si>
+    <t>坑道王・アイアンレイバー</t>
+  </si>
+  <si>
+    <t>水苔スライム</t>
+  </si>
+  <si>
+    <t>湿潤ラット</t>
+  </si>
+  <si>
+    <t>水没スケルトン</t>
+  </si>
+  <si>
+    <t>沼トカゲ</t>
+  </si>
+  <si>
+    <t>下水ワーム</t>
+  </si>
+  <si>
+    <t>水路の守護獣・モスガーディアン</t>
+  </si>
+  <si>
+    <t>腐骨スケルトン</t>
+  </si>
+  <si>
+    <t>墓守ゾンビ</t>
+  </si>
+  <si>
+    <t>霊火ウィスプ</t>
+  </si>
+  <si>
+    <t>墓標ゴーレム</t>
+  </si>
+  <si>
+    <t>彷徨う亡霊</t>
+  </si>
+  <si>
+    <t>死霊侯・ネクロロード</t>
+  </si>
+  <si>
+    <t>落石クラブ</t>
+  </si>
+  <si>
+    <t>岩皮バット</t>
+  </si>
+  <si>
+    <t>洞穴トロール</t>
+  </si>
+  <si>
+    <t>地割れスライム</t>
+  </si>
+  <si>
+    <t>採掘ビートル</t>
+  </si>
+  <si>
+    <t>洞窟崩壊獣・ロックタイタン</t>
+  </si>
+  <si>
+    <t>火花インプ</t>
+  </si>
+  <si>
+    <t>溶岩スライム</t>
+  </si>
+  <si>
+    <t>焼骨スケルトン</t>
+  </si>
+  <si>
+    <t>火蜥蜴</t>
+  </si>
+  <si>
+    <t>灰翼コウモリ</t>
+  </si>
+  <si>
+    <t>灼熱竜・マグナ＝ドラコ</t>
+  </si>
+  <si>
+    <t>氷晶スライム</t>
+  </si>
+  <si>
+    <t>凍骨スケルトン</t>
+  </si>
+  <si>
+    <t>雪皮ウルフ</t>
+  </si>
+  <si>
+    <t>氷刃バット</t>
+  </si>
+  <si>
+    <t>霜ゴーレム</t>
+  </si>
+  <si>
+    <t>氷王・フロストコロッサス</t>
+  </si>
+  <si>
+    <t>風刃バード</t>
+  </si>
+  <si>
+    <t>峡谷ゴブリン</t>
+  </si>
+  <si>
+    <t>突風スライム</t>
+  </si>
+  <si>
+    <t>崖跳ねヤギ</t>
+  </si>
+  <si>
+    <t>空裂ウィスプ</t>
+  </si>
+  <si>
+    <t>暴風獣・テンペストハウル</t>
+  </si>
+  <si>
+    <t>放電スライム</t>
+  </si>
+  <si>
+    <t>雷骨スケルトン</t>
+  </si>
+  <si>
+    <t>スパークインプ</t>
+  </si>
+  <si>
+    <t>電撃ビートル</t>
+  </si>
+  <si>
+    <t>雷羽バード</t>
+  </si>
+  <si>
+    <t>雷帝・ヴォルトタイラント</t>
+  </si>
+  <si>
+    <t>砂塵スケルトン</t>
+  </si>
+  <si>
+    <t>遺跡スカラベ</t>
+  </si>
+  <si>
+    <t>砂蛇</t>
+  </si>
+  <si>
+    <t>石像ガーディアン</t>
+  </si>
+  <si>
+    <t>流砂スライム</t>
+  </si>
+  <si>
+    <t>砂王・デザートファラオ</t>
+  </si>
+  <si>
+    <t>毒胞スライム</t>
+  </si>
+  <si>
+    <t>腐葉スケルトン</t>
+  </si>
+  <si>
+    <t>毒牙ウルフ</t>
+  </si>
+  <si>
+    <t>毒霧ウィスプ</t>
+  </si>
+  <si>
+    <t>腐根トレント</t>
+  </si>
+  <si>
+    <t>瘴気王・ヴェノムドライアド</t>
+  </si>
+  <si>
+    <t>呪符スケルトン</t>
+  </si>
+  <si>
+    <t>暴走グリモア</t>
+  </si>
+  <si>
+    <t>インクスライム</t>
+  </si>
+  <si>
+    <t>魔導ゴーレム</t>
+  </si>
+  <si>
+    <t>詠唱ウィスプ</t>
+  </si>
+  <si>
+    <t>禁書管理者・アーカイヴロード</t>
+  </si>
+  <si>
+    <t>影兵スケルトン</t>
+  </si>
+  <si>
+    <t>シャドウインプ</t>
+  </si>
+  <si>
+    <t>闇染みスライム</t>
+  </si>
+  <si>
+    <t>影走りハウンド</t>
+  </si>
+  <si>
+    <t>暗幕ウィスプ</t>
+  </si>
+  <si>
+    <t>影王・ナイトステッチャー</t>
+  </si>
+  <si>
+    <t>鏡像スケルトン</t>
+  </si>
+  <si>
+    <t>分裂スライム</t>
+  </si>
+  <si>
+    <t>反射ビートル</t>
+  </si>
+  <si>
+    <t>虚像インプ</t>
+  </si>
+  <si>
+    <t>鏡霊ウィスプ</t>
+  </si>
+  <si>
+    <t>迷宮主・リフレクタス</t>
+  </si>
+  <si>
+    <t>血晶スケルトン</t>
+  </si>
+  <si>
+    <t>供物ゾンビ</t>
+  </si>
+  <si>
+    <t>血滴スライム</t>
+  </si>
+  <si>
+    <t>血祭インプ</t>
+  </si>
+  <si>
+    <t>結晶ゴーレム</t>
+  </si>
+  <si>
+    <t>血王・サクリファイスロード</t>
+  </si>
+  <si>
+    <t>結界兵スケルトン</t>
+  </si>
+  <si>
+    <t>結界スライム</t>
+  </si>
+  <si>
+    <t>深層インプ</t>
+  </si>
+  <si>
+    <t>結界ビートル</t>
+  </si>
+  <si>
+    <t>防護ウィスプ</t>
+  </si>
+  <si>
+    <t>結界核・プロテクトコア</t>
+  </si>
+  <si>
+    <t>歪時スケルトン</t>
+  </si>
+  <si>
+    <t>加速インプ</t>
+  </si>
+  <si>
+    <t>減速スライム</t>
+  </si>
+  <si>
+    <t>時喰いワーム</t>
+  </si>
+  <si>
+    <t>歪曲ウィスプ</t>
+  </si>
+  <si>
+    <t>時王・クロノディストータ</t>
+  </si>
+  <si>
+    <t>星殻スケルトン</t>
+  </si>
+  <si>
+    <t>星光スライム</t>
+  </si>
+  <si>
+    <t>宇宙インプ</t>
+  </si>
+  <si>
+    <t>重力ビートル</t>
+  </si>
+  <si>
+    <t>星霊ウィスプ</t>
+  </si>
+  <si>
+    <t>星喰獣・アストラデヴァウラー</t>
+  </si>
+  <si>
+    <t>契約兵スケルトン</t>
+  </si>
+  <si>
+    <t>契約インプ</t>
+  </si>
+  <si>
+    <t>誓約スライム</t>
+  </si>
+  <si>
+    <t>試練ゴーレム</t>
+  </si>
+  <si>
+    <t>契約ウィスプ</t>
+  </si>
+  <si>
+    <t>契約王・オースブリンガー</t>
+  </si>
+  <si>
+    <t>反復スケルトン</t>
+  </si>
+  <si>
+    <t>無限スライム</t>
+  </si>
+  <si>
+    <t>反復インプ</t>
+  </si>
+  <si>
+    <t>ループビートル</t>
+  </si>
+  <si>
+    <t>回廊ウィスプ</t>
+  </si>
+  <si>
+    <t>循環王・インフィニティループ</t>
+  </si>
+  <si>
+    <t>混成スケルトン</t>
+  </si>
+  <si>
+    <t>破滅インプ</t>
+  </si>
+  <si>
+    <t>暴走スライム</t>
+  </si>
+  <si>
+    <t>前哨ゴーレム</t>
+  </si>
+  <si>
+    <t>崩壊ウィスプ</t>
+  </si>
+  <si>
+    <t>破滅将・アポカリプスガード</t>
+  </si>
+  <si>
+    <t>深淵骨スケルトン</t>
+  </si>
+  <si>
+    <t>侵食スライム</t>
+  </si>
+  <si>
+    <t>深淵インプ</t>
+  </si>
+  <si>
+    <t>侵食ビートル</t>
+  </si>
+  <si>
+    <t>深淵ウィスプ</t>
+  </si>
+  <si>
+    <t>深淵王・アビスオーバーロード</t>
+  </si>
+  <si>
+    <t>無色スケルトン</t>
+  </si>
+  <si>
+    <t>虚無スライム</t>
+  </si>
+  <si>
+    <t>無音インプ</t>
+  </si>
+  <si>
+    <t>虚無ゴーレム</t>
+  </si>
+  <si>
+    <t>空白ウィスプ</t>
+  </si>
+  <si>
+    <t>虚無監視者・ナッシングウォーデン</t>
+  </si>
+  <si>
+    <t>黒曜骨兵</t>
+  </si>
+  <si>
+    <t>戦場インプ</t>
+  </si>
+  <si>
+    <t>黒刃スライム</t>
+  </si>
+  <si>
+    <t>黒曜ビートル</t>
+  </si>
+  <si>
+    <t>血煙ウィスプ</t>
+  </si>
+  <si>
+    <t>戦王・オブシディアンロード</t>
+  </si>
+  <si>
+    <t>神骨スケルトン</t>
+  </si>
+  <si>
+    <t>神骸スライム</t>
+  </si>
+  <si>
+    <t>眷属インプ</t>
+  </si>
+  <si>
+    <t>神殻ゴーレム</t>
+  </si>
+  <si>
+    <t>神光ウィスプ</t>
+  </si>
+  <si>
+    <t>神骸王・ディヴァインレムナント</t>
+  </si>
+  <si>
+    <t>混沌骨スケルトン</t>
+  </si>
+  <si>
+    <t>混沌スライム</t>
+  </si>
+  <si>
+    <t>終焉インプ</t>
+  </si>
+  <si>
+    <t>崩壊ゴーレム</t>
+  </si>
+  <si>
+    <t>終焉ウィスプ</t>
+  </si>
+  <si>
+    <t>終焉竜・エンドオブカタストロフ</t>
+  </si>
+  <si>
+    <t>スライム・ルミナ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>若葉精モックル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>棍棒ゴブリン・ガズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灰牙狼ヴァルグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剛牙猪グランボア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>翠羽ハーピー・フィアナ</t>
+  </si>
+  <si>
+    <t>リフィル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モスガルド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エルドラン樹王</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シルヴェリオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヴァルグリーフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミフェリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポポグリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィルゼッタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガンロック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヴェルナガ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>嶺殻獣グランモルド</t>
+  </si>
+  <si>
+    <t>ガルド・ヴァラン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苔耳獣モスピコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灯茸精チロルーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>裂晶獣クラグレイス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古灯機兵ガルドランプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍾甲巨獣グラドガーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>封晶古竜ヴァル＝セレグナ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミストフェルム</t>
+  </si>
+  <si>
+    <t>ヴォルガスト</t>
+  </si>
+  <si>
+    <t>ライゼルヴァーン</t>
+  </si>
+  <si>
+    <t>フロレシア</t>
+  </si>
+  <si>
+    <t>グランテラドン</t>
+  </si>
+  <si>
+    <t>セレスクリオス</t>
+  </si>
+  <si>
+    <t>万彩霊獣ヴァルグラディオ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>獄晶王グラヴァルド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冥蝕王ヴァルグレイヴ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリスタモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガレキモグリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>裂晶翼ヴェルキア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>封鎖魔兵ガルドーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>迷宮喰獣ラビリオス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破界王ゼル＝アビス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミネグラ</t>
+  </si>
+  <si>
+    <t>ヴァルゼイン</t>
+  </si>
+  <si>
+    <t>ネフィレイア</t>
+  </si>
+  <si>
+    <t>グラディオル</t>
+  </si>
+  <si>
+    <t>ゼルガディス</t>
+  </si>
+  <si>
+    <t>フィルメリア</t>
+  </si>
+  <si>
+    <t>アズレフィア</t>
+  </si>
+  <si>
+    <t>ヴァルグレイド</t>
+  </si>
+  <si>
+    <t>ノクティレム</t>
+  </si>
+  <si>
+    <t>シェルディア</t>
+  </si>
+  <si>
+    <t>リュセリアス</t>
+  </si>
+  <si>
+    <t>ヴェルグノア</t>
+  </si>
+  <si>
+    <t>グラヴェリア</t>
+  </si>
+  <si>
+    <t>エルドレシア</t>
+  </si>
+  <si>
+    <t>オルフェギオン</t>
+  </si>
+  <si>
+    <t>セレグノス</t>
+  </si>
+  <si>
+    <t>ヴァルディオス</t>
+  </si>
+  <si>
+    <t>ネブラキア</t>
+  </si>
+  <si>
+    <t>ゼフィラグナ</t>
+  </si>
+  <si>
+    <t>ヴェルセディオ</t>
+  </si>
+  <si>
+    <t>グロメディア</t>
+  </si>
+  <si>
+    <t>ルクシエル</t>
+  </si>
+  <si>
+    <t>ザルヴェイン</t>
+  </si>
+  <si>
+    <t>バルグレシオ</t>
+  </si>
+  <si>
+    <t>セレフィネア</t>
+  </si>
+  <si>
+    <t>グランヴェリオ</t>
+  </si>
+  <si>
+    <t>ゼルアラクス</t>
+  </si>
+  <si>
+    <t>ノクティエル</t>
+  </si>
+  <si>
+    <t>ヴァルグディア</t>
+  </si>
+  <si>
+    <t>アステルヴェイン</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,6 +2274,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -65,7 +2291,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,20 +2314,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,15 +2687,2169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026CAAB4-E721-4B0C-B2B7-A4F02A2A1DAB}">
+  <dimension ref="A1:A370"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.25" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A126" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A147" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A154" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A178" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A179" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A180" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A181" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A182" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A183" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A185" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A186" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A187" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A188" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A189" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A190" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A191" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A192" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A193" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A194" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A195" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A196" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A197" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A198" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A199" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A200" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A201" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A202" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A203" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A204" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A205" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A206" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A207" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A208" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A213" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A214" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A215" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A216" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A217" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A218" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A219" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A220" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A221" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A222" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A224" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A225" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A227" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A228" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A229" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A231" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A232" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A233" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A234" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A235" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A237" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A238" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A239" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A240" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A241" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A242" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A243" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A244" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A245" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A246" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A247" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A248" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A249" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A250" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A251" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A252" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A253" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A254" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A255" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A256" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A257" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A258" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A259" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A260" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A261" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A262" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A263" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A264" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A265" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A266" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A267" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A268" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A269" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A270" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A271" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A272" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A273" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A274" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A275" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A276" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A277" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A278" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A279" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A280" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A281" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A282" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A283" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A284" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A285" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A286" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A287" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A288" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A289" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A290" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A291" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A292" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A293" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A294" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A295" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A296" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A297" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A298" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A299" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A300" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A301" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A302" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A303" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A304" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A305" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A306" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A307" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A308" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A309" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A310" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A311" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A312" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A313" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A314" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A315" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A316" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A317" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A318" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A319" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A320" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A321" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A322" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A323" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A324" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A325" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A326" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A327" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A328" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A329" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A330" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A331" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A332" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A333" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A334" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A335" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A336" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A337" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A338" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A339" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A340" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A341" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A342" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A343" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A344" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A345" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A346" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A347" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A348" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A349" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A350" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A351" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A352" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A353" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A354" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A355" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A356" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A357" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A358" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A359" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A360" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A361" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A362" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A363" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A364" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A365" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A366" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A367" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A368" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A369" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A370" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2789E06E-BA01-416D-B10A-FD884F219AEC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="12.5" style="1"/>
   </cols>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F20D1F1-1762-4F84-A326-8DC0937774F6}">
+  <dimension ref="A1:A62"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="217.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2"/>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
